--- a/data/trans_orig/IP07_C11_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C11_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener problemas para dormir en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,47 +720,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3379</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2095</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7717</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>10498</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>582</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8793</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3461</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4004</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4033</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -946,107 +946,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4260</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4512</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>4028</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>3882</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5213</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10677</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3729</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1385</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8360</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,82%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10429</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15252</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40853</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34684</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44817</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,95%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>72,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>24659</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19614</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28082</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>79,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>62,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41888</t>
+          <t>26627</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35923</t>
+          <t>21204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45904</t>
+          <t>30781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>66548</t>
+          <t>67480</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58861</t>
+          <t>59026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72917</t>
+          <t>73471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5502</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4380</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1498</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5373</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3358</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10272</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>10,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1159</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1201</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3901</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4247</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>829</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>9108</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3631</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1872</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5277</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>366</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>786</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12776</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7175</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20241</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,54%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8393</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4247</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12762</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15,65%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12346</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19030</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20739</t>
+          <t>21940</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13837</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29868</t>
+          <t>31823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>83580</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75781</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>90578</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>82,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,87%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>41479</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>36442</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>46291</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>77,34%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>85056</t>
+          <t>44059</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77180</t>
+          <t>37802</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91516</t>
+          <t>48762</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>126535</t>
+          <t>127639</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116240</t>
+          <t>118127</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>134405</t>
+          <t>136069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>357</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>936</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -2197,107 +2197,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2239</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2397</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>6959</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>14,11%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2397</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>6266</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6126</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>2239</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6417</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -2310,107 +2310,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>1108</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4526</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4263</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>4317</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1108</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>4398</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6007</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>23661</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18,67%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>36,5%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>30995</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>4532</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>56287</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>42,94%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>77,98%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11468</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22704</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>42464</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>10537</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>85281</t>
+          <t>31952</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>52367</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>40840</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>58507</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>80,78%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>63,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>90,25%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>37008</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>13653</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>61332</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>51,27%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>18,91%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>84,97%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>53083</t>
+          <t>37917</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42014</t>
+          <t>30096</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58977</t>
+          <t>42719</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>90091</t>
+          <t>90284</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49022</t>
+          <t>77017</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115867</t>
+          <t>98675</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6672</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>11,95%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1738</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5551</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3725</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1564</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1738</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>5053</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>6450</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3945</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>1324</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>8760</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>564</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>619</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10082</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>14121</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>9160</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>20839</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>25,3%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>16,41%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>37,33%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>8986</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>4984</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>14327</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>26,79%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21979</t>
+          <t>14888</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>23958</t>
+          <t>23501</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>16683</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33681</t>
+          <t>32122</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>33597</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>26198</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>40015</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>60,19%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>46,93%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>71,69%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>38599</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>32811</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>43510</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>72,17%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>61,35%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>81,35%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>33158</t>
+          <t>40867</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25822</t>
+          <t>34726</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39333</t>
+          <t>46519</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>71757</t>
+          <t>74464</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>61306</t>
+          <t>64793</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>80151</t>
+          <t>83246</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,87%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>4510</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>9456</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>11524</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14624</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21086</t>
+          <t>21076</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>3897</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>8931</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>5576</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>2519</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>12080</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,22 +3749,22 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>44215</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>33013</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>60148</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>22,27%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>52104</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>26081</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>109831</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>24,76%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>52,18%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>43592</t>
+          <t>29499</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>31683</t>
+          <t>21119</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>57711</t>
+          <t>41169</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>95697</t>
+          <t>73714</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>68156</t>
+          <t>58318</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>165121</t>
+          <t>92530</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>210396</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>193599</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>223193</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>77,9%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>71,68%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>82,63%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>141745</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>92958</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>167316</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>67,35%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>44,17%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>79,5%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>213186</t>
+          <t>149470</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>197874</t>
+          <t>138189</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>226249</t>
+          <t>160236</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>354931</t>
+          <t>359867</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>292251</t>
+          <t>338542</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>382548</t>
+          <t>377405</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
